--- a/Sindhi Muslim/Staff Record/Staff Record.xlsx
+++ b/Sindhi Muslim/Staff Record/Staff Record.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Staff Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214552A8-B8B2-4CB7-8539-D26940422539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0229B684-F806-4E96-9B82-81A9B4292286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="102">
   <si>
     <t>Employee Attendance Sheet</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t xml:space="preserve">Government High School Sindhi Jamaat Cooperative Housing Society, Bin Qasim Town Karachi </t>
+  </si>
+  <si>
+    <t>The Nexus</t>
   </si>
 </sst>
 </file>
@@ -808,7 +811,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -944,6 +947,24 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -954,6 +975,63 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -965,29 +1043,29 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -995,82 +1073,10 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1091,9 +1097,7 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1123,16 +1127,6 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1148,6 +1142,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1471,142 +1475,142 @@
   <sheetData>
     <row r="2" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="90" t="str">
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="53" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="E3" s="90" t="str">
+      <c r="E3" s="53" t="str">
         <f t="shared" ref="E3:AH3" si="0">TEXT(E4,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="F3" s="90" t="str">
+      <c r="F3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="G3" s="90" t="str">
+      <c r="G3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="H3" s="90" t="str">
+      <c r="H3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="I3" s="90" t="str">
+      <c r="I3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="J3" s="90" t="str">
+      <c r="J3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="K3" s="90" t="str">
+      <c r="K3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="L3" s="90" t="str">
+      <c r="L3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="M3" s="90" t="str">
+      <c r="M3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="N3" s="90" t="str">
+      <c r="N3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="O3" s="90" t="str">
+      <c r="O3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="P3" s="90" t="str">
+      <c r="P3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="Q3" s="90" t="str">
+      <c r="Q3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="R3" s="90" t="str">
+      <c r="R3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="S3" s="90" t="str">
+      <c r="S3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="T3" s="90" t="str">
+      <c r="T3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="U3" s="90" t="str">
+      <c r="U3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="V3" s="90" t="str">
+      <c r="V3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="W3" s="90" t="str">
+      <c r="W3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="X3" s="90" t="str">
+      <c r="X3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="Y3" s="90" t="str">
+      <c r="Y3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="Z3" s="90" t="str">
+      <c r="Z3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="AA3" s="90" t="str">
+      <c r="AA3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AB3" s="90" t="str">
+      <c r="AB3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="AC3" s="90" t="str">
+      <c r="AC3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AD3" s="90" t="str">
+      <c r="AD3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="AE3" s="90" t="str">
+      <c r="AE3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AF3" s="90" t="str">
+      <c r="AF3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="AG3" s="90" t="str">
+      <c r="AG3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="AH3" s="90" t="str">
+      <c r="AH3" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AI3" s="55" t="s">
+      <c r="AI3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="55"/>
-      <c r="AK3" s="55"/>
-      <c r="AL3" s="55"/>
-      <c r="AM3" s="56"/>
+      <c r="AJ3" s="61"/>
+      <c r="AK3" s="61"/>
+      <c r="AL3" s="61"/>
+      <c r="AM3" s="62"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -1810,7 +1814,7 @@
       <c r="AC5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD5" s="91"/>
+      <c r="AD5" s="54"/>
       <c r="AE5" s="4" t="s">
         <v>6</v>
       </c>
@@ -1839,7 +1843,7 @@
         <f>COUNTBLANK(D5:AH5)</f>
         <v>4</v>
       </c>
-      <c r="AM5" s="92">
+      <c r="AM5" s="55">
         <f>AI5+AK5+AL5</f>
         <v>31</v>
       </c>
@@ -1927,7 +1931,7 @@
       <c r="AC6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD6" s="91"/>
+      <c r="AD6" s="54"/>
       <c r="AE6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1956,7 +1960,7 @@
         <f t="shared" ref="AL6:AL13" si="4">COUNTBLANK(D6:AH6)</f>
         <v>4</v>
       </c>
-      <c r="AM6" s="92">
+      <c r="AM6" s="55">
         <f t="shared" ref="AM6:AM13" si="5">AI6+AK6+AL6</f>
         <v>31</v>
       </c>
@@ -2044,7 +2048,7 @@
       <c r="AC7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AD7" s="91" t="s">
+      <c r="AD7" s="54" t="s">
         <v>7</v>
       </c>
       <c r="AE7" s="4" t="s">
@@ -2075,7 +2079,7 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="AM7" s="92">
+      <c r="AM7" s="55">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
@@ -2163,7 +2167,7 @@
       <c r="AC8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD8" s="91"/>
+      <c r="AD8" s="54"/>
       <c r="AE8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2192,7 +2196,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AM8" s="92">
+      <c r="AM8" s="55">
         <f t="shared" si="5"/>
         <v>29</v>
       </c>
@@ -2280,7 +2284,7 @@
       <c r="AC9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AD9" s="91" t="s">
+      <c r="AD9" s="54" t="s">
         <v>7</v>
       </c>
       <c r="AE9" s="4" t="s">
@@ -2311,7 +2315,7 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="AM9" s="92">
+      <c r="AM9" s="55">
         <f t="shared" si="5"/>
         <v>26</v>
       </c>
@@ -2399,7 +2403,7 @@
       <c r="AC10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD10" s="91"/>
+      <c r="AD10" s="54"/>
       <c r="AE10" s="4" t="s">
         <v>6</v>
       </c>
@@ -2428,7 +2432,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AM10" s="92">
+      <c r="AM10" s="55">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
@@ -2516,7 +2520,7 @@
       <c r="AC11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD11" s="91"/>
+      <c r="AD11" s="54"/>
       <c r="AE11" s="4" t="s">
         <v>6</v>
       </c>
@@ -2545,7 +2549,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AM11" s="92">
+      <c r="AM11" s="55">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
@@ -2632,7 +2636,7 @@
       <c r="AC12" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="AD12" s="93"/>
+      <c r="AD12" s="56"/>
       <c r="AE12" s="14" t="s">
         <v>6</v>
       </c>
@@ -2661,7 +2665,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AM12" s="92">
+      <c r="AM12" s="55">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
@@ -2748,7 +2752,7 @@
       <c r="AC13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AD13" s="94"/>
+      <c r="AD13" s="57"/>
       <c r="AE13" s="6" t="s">
         <v>6</v>
       </c>
@@ -2777,149 +2781,149 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AM13" s="95">
+      <c r="AM13" s="58">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A17" s="53" t="s">
+      <c r="A17" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="90" t="str">
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="53" t="str">
         <f>TEXT(D18,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="E17" s="90" t="str">
+      <c r="E17" s="53" t="str">
         <f t="shared" ref="E17:AH17" si="7">TEXT(E18,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="F17" s="90" t="str">
+      <c r="F17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Thu</v>
       </c>
-      <c r="G17" s="90" t="str">
+      <c r="G17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Fri</v>
       </c>
-      <c r="H17" s="90" t="str">
+      <c r="H17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Sat</v>
       </c>
-      <c r="I17" s="90" t="str">
+      <c r="I17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Sun</v>
       </c>
-      <c r="J17" s="90" t="str">
+      <c r="J17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Mon</v>
       </c>
-      <c r="K17" s="90" t="str">
+      <c r="K17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Tue</v>
       </c>
-      <c r="L17" s="90" t="str">
+      <c r="L17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Wed</v>
       </c>
-      <c r="M17" s="90" t="str">
+      <c r="M17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Thu</v>
       </c>
-      <c r="N17" s="90" t="str">
+      <c r="N17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Fri</v>
       </c>
-      <c r="O17" s="90" t="str">
+      <c r="O17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Sat</v>
       </c>
-      <c r="P17" s="90" t="str">
+      <c r="P17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Sun</v>
       </c>
-      <c r="Q17" s="90" t="str">
+      <c r="Q17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Mon</v>
       </c>
-      <c r="R17" s="90" t="str">
+      <c r="R17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Tue</v>
       </c>
-      <c r="S17" s="90" t="str">
+      <c r="S17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Wed</v>
       </c>
-      <c r="T17" s="90" t="str">
+      <c r="T17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Thu</v>
       </c>
-      <c r="U17" s="90" t="str">
+      <c r="U17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Fri</v>
       </c>
-      <c r="V17" s="90" t="str">
+      <c r="V17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Sat</v>
       </c>
-      <c r="W17" s="90" t="str">
+      <c r="W17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Sun</v>
       </c>
-      <c r="X17" s="90" t="str">
+      <c r="X17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Mon</v>
       </c>
-      <c r="Y17" s="90" t="str">
+      <c r="Y17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Tue</v>
       </c>
-      <c r="Z17" s="90" t="str">
+      <c r="Z17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Wed</v>
       </c>
-      <c r="AA17" s="90" t="str">
+      <c r="AA17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Thu</v>
       </c>
-      <c r="AB17" s="90" t="str">
+      <c r="AB17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Fri</v>
       </c>
-      <c r="AC17" s="90" t="str">
+      <c r="AC17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Sat</v>
       </c>
-      <c r="AD17" s="90" t="str">
+      <c r="AD17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Sun</v>
       </c>
-      <c r="AE17" s="90" t="str">
+      <c r="AE17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Mon</v>
       </c>
-      <c r="AF17" s="90" t="str">
+      <c r="AF17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Tue</v>
       </c>
-      <c r="AG17" s="90" t="str">
+      <c r="AG17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Wed</v>
       </c>
-      <c r="AH17" s="90" t="str">
+      <c r="AH17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Thu</v>
       </c>
-      <c r="AI17" s="55" t="s">
+      <c r="AI17" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="AJ17" s="55"/>
-      <c r="AK17" s="55"/>
-      <c r="AL17" s="55"/>
-      <c r="AM17" s="56"/>
+      <c r="AJ17" s="61"/>
+      <c r="AK17" s="61"/>
+      <c r="AL17" s="61"/>
+      <c r="AM17" s="62"/>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -3884,15 +3888,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D17:AH25">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:AH25">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3902,7 +3906,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D9966C9-EF06-414E-BAA0-6ADB4FC6B171}">
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -3918,46 +3922,47 @@
     <col min="12" max="12" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
     <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+    <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="97" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="98"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="99"/>
     </row>
-    <row r="2" spans="1:14" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="99" t="s">
+    <row r="2" spans="1:18" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="100" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="101"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="102"/>
     </row>
-    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="73" t="s">
         <v>88</v>
       </c>
@@ -3975,7 +3980,7 @@
       <c r="M4" s="74"/>
       <c r="N4" s="75"/>
     </row>
-    <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19"/>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -3991,85 +3996,85 @@
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="87" t="s">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="76" t="s">
+      <c r="B6" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="76" t="s">
+      <c r="D6" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="57" t="s">
+      <c r="E6" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="F6" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="57" t="s">
+      <c r="H6" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="102" t="s">
+      <c r="I6" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="102"/>
-      <c r="M6" s="70" t="s">
+      <c r="J6" s="89"/>
+      <c r="K6" s="89"/>
+      <c r="L6" s="89"/>
+      <c r="M6" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="N6" s="60" t="s">
+      <c r="N6" s="66" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="88"/>
-      <c r="B7" s="63"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="68" t="s">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="77"/>
+      <c r="B7" s="80"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="68" t="s">
+      <c r="J7" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="68" t="s">
+      <c r="K7" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="L7" s="66" t="s">
+      <c r="L7" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="M7" s="71"/>
-      <c r="N7" s="61"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="67"/>
     </row>
-    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="89"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="72"/>
-      <c r="N8" s="62"/>
+    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="78"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="84"/>
+      <c r="I8" s="94"/>
+      <c r="J8" s="94"/>
+      <c r="K8" s="94"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="92"/>
+      <c r="N8" s="68"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
         <v>42</v>
       </c>
@@ -4114,8 +4119,20 @@
         <f>(H9/31)*J9</f>
         <v>22000</v>
       </c>
+      <c r="O9" t="s">
+        <v>101</v>
+      </c>
+      <c r="P9" s="103">
+        <v>43313</v>
+      </c>
+      <c r="Q9" s="103">
+        <v>44682</v>
+      </c>
+      <c r="R9">
+        <v>3000266949</v>
+      </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>43</v>
       </c>
@@ -4161,7 +4178,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
         <v>44</v>
       </c>
@@ -4204,7 +4221,7 @@
         <v>11500</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
         <v>62</v>
       </c>
@@ -4249,7 +4266,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
         <v>45</v>
       </c>
@@ -4293,7 +4310,7 @@
         <v>12500</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
         <v>46</v>
       </c>
@@ -4339,7 +4356,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
         <v>47</v>
       </c>
@@ -4385,7 +4402,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
         <v>90</v>
       </c>
@@ -4544,82 +4561,82 @@
       <c r="N21" s="19"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="87" t="s">
+      <c r="A22" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="76" t="s">
+      <c r="B22" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="76" t="s">
+      <c r="C22" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="76" t="s">
+      <c r="D22" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="57" t="s">
+      <c r="E22" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="57" t="s">
+      <c r="F22" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="G22" s="81" t="s">
+      <c r="G22" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="H22" s="81" t="s">
+      <c r="H22" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="I22" s="65" t="s">
+      <c r="I22" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="J22" s="65"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="65"/>
-      <c r="M22" s="84" t="s">
+      <c r="J22" s="88"/>
+      <c r="K22" s="88"/>
+      <c r="L22" s="88"/>
+      <c r="M22" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="N22" s="60" t="s">
+      <c r="N22" s="66" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="88"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="82"/>
-      <c r="H23" s="82"/>
-      <c r="I23" s="77" t="s">
+      <c r="A23" s="77"/>
+      <c r="B23" s="80"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="80"/>
+      <c r="G23" s="86"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="J23" s="77" t="s">
+      <c r="J23" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="K23" s="77" t="s">
+      <c r="K23" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="L23" s="79" t="s">
+      <c r="L23" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="M23" s="85"/>
-      <c r="N23" s="61"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="67"/>
     </row>
     <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="89"/>
-      <c r="B24" s="64"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="80"/>
-      <c r="M24" s="86"/>
-      <c r="N24" s="62"/>
+      <c r="A24" s="78"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="81"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="84"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="87"/>
+      <c r="H24" s="87"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="65"/>
+      <c r="N24" s="68"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
@@ -4943,12 +4960,24 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="M22:M24"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
     <mergeCell ref="A20:N20"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="B22:B24"/>
@@ -4959,24 +4988,12 @@
     <mergeCell ref="G22:G24"/>
     <mergeCell ref="H22:H24"/>
     <mergeCell ref="I22:L22"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="M22:M24"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="L23:L24"/>
   </mergeCells>
   <conditionalFormatting sqref="B9:M9 B10:C13 M10:M16 D10:L17 C14:C16 F25:F31 G26:I30 D26:E31 K26:M31 G31:J31">
     <cfRule type="expression" dxfId="2" priority="3">
